--- a/AAII_Financials/Quarterly/MKL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MKL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="92">
   <si>
     <t>MKL</t>
   </si>
@@ -656,344 +656,351 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5186000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2823000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4220000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4367400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4602800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3399100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3841000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4611300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3701800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4466700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4642500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3375200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4142500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3643400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4210700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3066100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1792200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2606200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3755500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2687700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3501200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2900400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3355700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2912100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3132000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>334900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2581500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2033100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2439100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2472500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1042900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2235900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1987000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1575500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1662600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1509600</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1482100</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1415000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1434900</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>1431300</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1923000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1906600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2112300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2036300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2062200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2002100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2026600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2034200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1942900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2026500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2325800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2102500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1885800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1848700</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1069,53 +1076,56 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>3263000</v>
+      </c>
+      <c r="E10" s="3">
         <v>916400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2107700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2331100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2540500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1397000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1814400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2577100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1759000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2440200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2316700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1272700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2256800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1794700</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1191,8 +1201,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,8 +1496,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1523,23 +1543,23 @@
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3">
         <v>80000</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>5</v>
+      <c r="U14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>5</v>
@@ -1547,32 +1567,32 @@
       <c r="X14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z14" s="3">
         <v>-13500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>46800</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC14" s="3">
         <v>325000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>10900</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>6700</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG14" s="3">
-        <v>0</v>
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AH14" s="3">
         <v>0</v>
@@ -1584,147 +1604,153 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
         <v>300</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>3400</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>600</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>3200</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>6300</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>43300</v>
+      </c>
+      <c r="E15" s="3">
         <v>43500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>42800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>44100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>51200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>46900</v>
-      </c>
-      <c r="I15" s="3">
-        <v>46500</v>
       </c>
       <c r="J15" s="3">
         <v>46500</v>
       </c>
       <c r="K15" s="3">
+        <v>46500</v>
+      </c>
+      <c r="L15" s="3">
         <v>44200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>44300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>44200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>47500</v>
-      </c>
-      <c r="O15" s="3">
-        <v>44400</v>
       </c>
       <c r="P15" s="3">
         <v>44400</v>
       </c>
       <c r="Q15" s="3">
+        <v>44400</v>
+      </c>
+      <c r="R15" s="3">
         <v>43800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>43400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>45500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>46000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>42000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>39300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>39700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>39600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>39000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>44700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>37800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>37900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>36000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>35700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>36300</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>40700</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>29700</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>27800</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>29600</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>28800</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>27300</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>18700</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>18000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>16800</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>17100</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3625600</v>
+      </c>
+      <c r="E17" s="3">
         <v>3096400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3424900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3357600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3495400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3116600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3245500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3239900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3291900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3130900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3510500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3302400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3172500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2889500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3154000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2999200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2969000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2646500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2580900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2445700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2421500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2154800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2211100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2219300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1889800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2141000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1838600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1777500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1772700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1677700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1975000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1680300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1675700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1470500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1483900</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1839500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1241600</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1287500</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1222500</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1278600</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1560300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-273300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>795100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1009800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1107300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>282500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>595500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1371300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>410000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1335800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1132100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>72800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>970100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>753900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1056700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>66900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1176800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-40300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1174600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>242000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1079700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>745600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1144600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>692800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1242200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-1806100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>742900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>255600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>666400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>794800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-932100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>555600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>311300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>105000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>178700</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-329900</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>240500</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>127500</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>212400</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>152700</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,618 +2085,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-54300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>11000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-19300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>191900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>72600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-180800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>111600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-8700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-51500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>81400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-39200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>15000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>32900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-103800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>113700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>105100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>23000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>13200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>48500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-12700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>24900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-87200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-65900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-21400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>79100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-59200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>53800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>25000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-21900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>41100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>1400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>86200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-22100</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>400</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>1800</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>900</v>
       </c>
-      <c r="AN20" s="3">
-        <v>0</v>
-      </c>
       <c r="AO20" s="3">
         <v>0</v>
       </c>
       <c r="AP20" s="3">
         <v>0</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1614000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-175500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>827000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1073200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>966600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>256800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>822800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1306200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>462900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1431600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1094900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>159600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>999500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>765400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>953300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>178500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1072300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>28800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1190500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>290100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1067200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>810000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1051800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>633700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1220700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-1689200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>684000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>308800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>687100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>813600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-889100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>555100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>398300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>111700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>187700</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>-327500</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>242600</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>144200</v>
       </c>
-      <c r="AO21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AP21" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ21" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>52400</v>
+      </c>
+      <c r="E22" s="3">
         <v>50900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>50000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>50700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>53100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>52100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>52800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>53400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>52600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>45500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>43900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>44600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>47200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>49400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>49000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>47300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>50100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>49700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>48200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>46500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>46600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>42400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>44400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>42700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>45400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>45000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>42700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>47500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>41300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>40300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>39500</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>38000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>36700</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>40100</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>35400</v>
-      </c>
-      <c r="AL22" s="3">
-        <v>31800</v>
       </c>
       <c r="AM22" s="3">
         <v>31800</v>
       </c>
       <c r="AN22" s="3">
+        <v>31800</v>
+      </c>
+      <c r="AO22" s="3">
         <v>33400</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>32200</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>33200</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1518300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-269900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>734200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>978400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>862400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>157800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>723500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1206400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>366100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1341700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1006800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>67500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>907900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>671500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>903900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>133200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1121800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-66900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1139600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>244100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1020400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>728100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1013100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>584100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1175400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1772100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>641000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>261900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>650200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>732700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-930500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>519000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>360700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>42800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>143700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-359900</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>209500</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>94000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>180200</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>119500</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>332900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-65600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>152100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>214700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>185200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>28400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>162100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>259400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>76200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>292600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>212700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>14200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>191900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>133700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>192400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>16500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-239000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-18100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>264600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>54400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>217100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>148400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>165600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>130000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>243700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-370700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>129500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>58000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>143700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>155200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-177100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>110000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>81200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>108400</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>44200</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-98900</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>58100</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>23000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>47500</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>36100</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1185500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-204400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>582100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>763800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>677200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>129300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>561400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>946900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>289900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1049200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>794100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>53300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>715900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>537800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>711500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>116800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-882800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-48800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>875100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>189700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>803300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>579700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>847400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>454000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>931700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1401400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>511500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>204000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>506500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>577500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-753400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>409000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>279600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-65600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>99400</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-261000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>151400</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>71000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>132700</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>83400</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1168000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-238700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>666100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>756000</v>
       </c>
-      <c r="G27" s="3">
-        <v>563100</v>
-      </c>
       <c r="H27" s="3">
+        <v>632300</v>
+      </c>
+      <c r="I27" s="3">
         <v>155100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>338200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>947500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>321000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>992600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>750400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>42000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>671800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>502100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>665900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>41900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-941300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-88700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>858500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>208000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>787800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>581600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>820900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>429100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>908700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1389800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>502700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>193400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>500600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>594800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-749800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>397400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>278600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-59300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>84800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-262400</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>144500</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>54700</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>128200</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>78900</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3236,8 +3297,8 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>5</v>
@@ -3254,12 +3315,12 @@
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL29" s="3">
         <v>339900</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E32" s="3">
         <v>54300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-11000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>19300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-191900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-72600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>180800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-111600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>8700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>51500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-81400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>39200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-15000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-32900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>103800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-113700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-105100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-23000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-13200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-48500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>12700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-24900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>87200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>65900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>21400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-79100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>59200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-53800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>21900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-41100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-86200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>22100</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-400</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-900</v>
       </c>
-      <c r="AN32" s="3">
-        <v>0</v>
-      </c>
       <c r="AO32" s="3">
         <v>0</v>
       </c>
       <c r="AP32" s="3">
         <v>0</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1168800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-212300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>576800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>751300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>657100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>121700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>549200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>905000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>267700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1025200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>769300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>42600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>695500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>488700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>665900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>41900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-941300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-88700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>858500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>208000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>787800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>581600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>820900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>429100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>908700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1389800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>502700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>193400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>500600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>594800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-749800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>397400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>278600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-59300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>424700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-262400</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>144500</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>54700</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>128200</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>78900</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1168800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-212300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>576800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>751300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>657100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>121700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>549200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>905000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>267700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1025200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>769300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>42600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>695500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>488700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>665900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>41900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-941300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-88700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>858500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>208000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>787800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>581600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>820900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>429100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>908700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1389800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>502700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>193400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>500600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>594800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-749800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>397400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>278600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-59300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>424700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-262400</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>144500</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>54700</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>128200</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>78900</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,175 +4305,179 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3423200</v>
+      </c>
+      <c r="E41" s="3">
         <v>3680500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3964700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4049200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3720200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4193700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3692700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3873000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3510600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3627100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3747100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4354900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4305900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4032000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4137400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3540700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3698900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3891100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3978500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3938600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3679400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3882400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4341700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4593000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4833700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3834700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3072800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2715500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2220800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2415400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2014200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2347000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1945400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2049000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2198500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>2076300</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>2315200</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1852700</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1738700</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>2156400</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2333400</v>
+      </c>
+      <c r="E42" s="3">
         <v>2026100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2033700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2115800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1894500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2099000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2524900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2355700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2787800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2617600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2571400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2252700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2039100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2487500</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4463,174 +4553,180 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4127500</v>
+      </c>
+      <c r="E43" s="3">
         <v>3808300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3989000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4268800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4551200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4282600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3640100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3909400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4227800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3608900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3455600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3557500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3695200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3192100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5027200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5242600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5252000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4627500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4212500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4241200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4335500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3732400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3382100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3461700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3741600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3348600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3263700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3439200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3651200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3293600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3023500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3178700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3211700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2915700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2667200</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1941300</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1934100</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1762000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1541600</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1666900</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3">
         <v>703400</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G44" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3">
         <v>731100</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N44" s="3">
         <v>617200</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4707,53 +4803,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>15813900</v>
+      </c>
+      <c r="E45" s="3">
         <v>15195800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>14616300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12989500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>12789700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>12617500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>11604800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>10746200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>9756700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>9575100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>9235500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>8534900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>8296000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>8585600</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4829,53 +4928,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>30252600</v>
+      </c>
+      <c r="E46" s="3">
         <v>28484700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>29019600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>27695600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>28094900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>27008300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>25640400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>25051200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>24661200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>22862000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>22577000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>22097900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>21757400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>21432100</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4951,174 +5053,180 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>31171200</v>
+      </c>
+      <c r="E47" s="3">
         <v>30246500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>31539900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>30047600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>29102500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>27975300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>28392600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>28509000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>26245900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>25723900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>24556500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>22109000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>21924300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>21008400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>22198000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>21101600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>21169400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>23044300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>23411200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>22941300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>22908400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>21093900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>19709900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>18325600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>16654000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>16058600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>18757900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>18728300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>18518100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>17297900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>16841800</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>18420600</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>18150900</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>17845100</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>18069500</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>17624900</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>17098700</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>17223500</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>16973500</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>16818200</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F48" s="3">
         <v>2158200</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J48" s="3">
         <v>2081400</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N48" s="3">
         <v>1928800</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
+      <c r="Q48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
@@ -5150,24 +5258,24 @@
       <c r="AA48" s="3">
         <v>0</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC48" s="3">
+      <c r="AB48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD48" s="3">
         <v>232700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>230500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>237400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>243400</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH48" s="3" t="s">
         <v>5</v>
       </c>
@@ -5177,8 +5285,8 @@
       <c r="AJ48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK48" s="3">
-        <v>0</v>
+      <c r="AK48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AL48" s="3">
         <v>0</v>
@@ -5195,130 +5303,136 @@
       <c r="AP48" s="3">
         <v>0</v>
       </c>
+      <c r="AQ48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5115200</v>
+      </c>
+      <c r="E49" s="3">
         <v>5192300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5274600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5372100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5419100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5368100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5071200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5215000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5292400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5133800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5144800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5242600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5317500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5343400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4386300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4483600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4498900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4547400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4721600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4414800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4302900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4341000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4387300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4425000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4472200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4001800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4047000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3846700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3885000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3928400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3964200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3024900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3054200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>3106900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>3133100</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>2415800</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>2023000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>1854500</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>1864800</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>1899300</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4724200</v>
+      </c>
+      <c r="E52" s="3">
         <v>4679000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>879900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4276300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4174700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4247500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>672400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3508000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3510100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3566600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>815100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3299200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3185000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3158300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1084100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1255200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1212500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1316500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>902500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>568400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>672400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>615500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>874900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>669500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>793700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>623700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>427500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>484300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>420700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>349000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>382300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>279900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>299000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>392700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>302400</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>279400</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>271000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>262000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>346400</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>384000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>71263100</v>
+      </c>
+      <c r="E54" s="3">
         <v>68602400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>68905100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>67391600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>66791200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>64599100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>61898000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>62283200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>59709600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>57286400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>55045700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>52748700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>52184100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>50942300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>49791300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>48421400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>47946800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>48985300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>48477100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>46696400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>45641500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>43043000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>41710100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>40170000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>39067600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>36048800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>37473800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>37036200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>36421600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>34736700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>33306300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>33958300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>33247000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>32866500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>32805000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>28519400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>27203300</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>26400700</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>25875300</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>26403600</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,53 +6145,54 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1678900</v>
+      </c>
+      <c r="E57" s="3">
         <v>1615800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1667900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1799700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1723800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1843000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1434900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1449000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1419000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1238000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1037700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>924600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>972200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>800400</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -6137,8 +6268,11 @@
       <c r="AP57" s="3">
         <v>0</v>
       </c>
+      <c r="AQ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -6146,11 +6280,11 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>140400</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
@@ -6259,175 +6393,181 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7923400</v>
+      </c>
+      <c r="E59" s="3">
         <v>7234900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7341300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8233800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9073400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7691700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7104300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7887100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>8244000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7154000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6671800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7196800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7072200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6570400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6890500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>7200300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>7039800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>6557700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>6000300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>6091300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>5933500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>5399200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4926700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4926800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4861800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4470600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4726600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4886700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4863300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4532700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3948400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4269400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>4117500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3956800</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>3633100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>2980300</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>2972400</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>2819000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>2495200</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>2731100</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9602300</v>
+      </c>
+      <c r="E60" s="3">
         <v>8850700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9149600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10033500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10797200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9534700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8539200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9336000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9663000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8392000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7709500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8121400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8044400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7370700</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6503,252 +6643,261 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4367700</v>
+      </c>
+      <c r="E61" s="3">
         <v>4382800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4873400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4284800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4364200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4390600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5054300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4356100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4399900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3855500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4437000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3769200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3813900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3896800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4103600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4131200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4502200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4428700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4361300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4268300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4160200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3564900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3484000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>3498300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>3606100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>3594000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>3534200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>3897000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>3625700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>3059000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>3009600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2993200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>3024300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>3048100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>3099200</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2471400</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>2485700</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>2581600</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>2574500</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>2589400</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>37821600</v>
+      </c>
+      <c r="E62" s="3">
         <v>36718700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>33879900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>34478000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>33761600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>32929300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>29235600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>30928300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>29221700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>28721400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>26173300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>26335400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>25622300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>25393500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>650700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>733500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>777700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>824200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>903000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>926000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>975500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>977600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1070000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1034100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>999400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>975500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>985700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1021200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1032700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1011600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1001500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1028700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1033500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1093400</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1072100</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1108900</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>1061300</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>1038300</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>1049700</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>1155700</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>51791700</v>
+      </c>
+      <c r="E66" s="3">
         <v>49952300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>49802900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>48796200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>48923100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>46854600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>44429000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>44620400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>43284500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>40968900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>39519800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>38226100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>37480600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>36661100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>36640200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>36127400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>35190600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>34884100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>33759700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>32679700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>31666500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>29879100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>28910300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>28276100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>27673100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>26328100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>26402900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>26412700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>26025200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>24940700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>24225600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>24174300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>23766200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>23542300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>23300900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>19610500</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>18248900</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>17747500</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>17414400</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>17876400</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7541,7 +7709,7 @@
         <v>0</v>
       </c>
       <c r="H70" s="3">
-        <v>591900</v>
+        <v>0</v>
       </c>
       <c r="I70" s="3">
         <v>591900</v>
@@ -7601,7 +7769,7 @@
         <v>591900</v>
       </c>
       <c r="AB70" s="3">
-        <v>0</v>
+        <v>591900</v>
       </c>
       <c r="AC70" s="3">
         <v>0</v>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>15593700</v>
+      </c>
+      <c r="E72" s="3">
         <v>14662400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>15034800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>14512700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>13839900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>13364800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>13380500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>13063400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>12329800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>12184900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>11353100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>10778600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>10819000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>10255400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>9832800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>9255700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>9289800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>10278400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>10446800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>9650400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>9503900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>8754800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>8195200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>7377100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6948500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6039500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>7457200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6988900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>6808200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>6338900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>5782300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>6576600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>6184300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>5927700</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>3776700</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>3378500</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>3666200</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>3557900</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>3526400</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>3433900</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>19005500</v>
+      </c>
+      <c r="E76" s="3">
         <v>18132000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>18597800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>18040700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>17318200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16556600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>16324000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>16422300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>15258100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>15137800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14392000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13407300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13593600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13152600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12559200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>11702000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>12164300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13509300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>14125500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>13424900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>13383100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>12572100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>12207900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>11302100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>10802700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>9720700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>11070900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>10623500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>10396400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>9796000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>9080700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>9784000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>9480900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>9324200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>9504100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>8908900</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>8954400</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>8653200</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>8460900</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>8527300</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1168800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-212300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>576800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>751300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>657100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>121700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>549200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>905000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>267700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1025200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>769300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>42600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>695500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>488700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>665900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>41900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-941300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-88700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>858500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>208000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>787800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>581600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>820900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>429100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>908700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1389800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>502700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>193400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>500600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>594800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-749800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>397400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>278600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-59300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>424700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-262400</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>144500</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>54700</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>128200</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>78900</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,53 +8990,54 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E83" s="3">
+      <c r="E83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F83" s="3">
         <v>160900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>-12900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>29600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>29700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>57500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>26900</v>
-      </c>
-      <c r="K83" s="3">
-        <v>27400</v>
       </c>
       <c r="L83" s="3">
         <v>27400</v>
       </c>
       <c r="M83" s="3">
+        <v>27400</v>
+      </c>
+      <c r="N83" s="3">
         <v>112900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>23700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>26500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>25000</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
       <c r="R83" s="3">
         <v>0</v>
       </c>
@@ -8914,8 +9113,11 @@
       <c r="AP83" s="3">
         <v>0</v>
       </c>
+      <c r="AQ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>428900</v>
+      </c>
+      <c r="E89" s="3">
         <v>15900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>662200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1218500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>504400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>376200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>493900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>890800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>578600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>630700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>822500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>955700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>724400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>284200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>829200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>959300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>506100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>414900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>651600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>809300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>495000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>318100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>476000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>772800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>423100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>65700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>562200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>462800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>230400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>18700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>129700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>455600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>249900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>57700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>259800</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>360800</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>226000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>11900</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>210300</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>254100</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-44300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-47300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-63100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-52400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-50600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-40700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-74000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-51900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-57200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-72000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-103500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-75600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-42300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-37200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-45400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-98700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-58800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-51700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-64500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-25000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-25100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-30700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-28500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-22100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-20800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-29900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-27900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-46200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-24500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-24800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-27700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-26500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-29000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-23400</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-24600</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-14500</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-19700</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-15900</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-28200</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-29900</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-197300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-348200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-554000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-719300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-109400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>192800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-514300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-326100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-994100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-564200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1361000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-969100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-265000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-108500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-386900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-880000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-353400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-50000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-205300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-495200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1159800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1077600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-534200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1031200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>147000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>906600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>122000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-135500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-863800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>342100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-344000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-7600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-377400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-68200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-650200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-531000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>399100</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>37700</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-550500</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-74200</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,8 +10455,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10266,8 +10500,8 @@
       <c r="P96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10344,8 +10578,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-341900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-79500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-111500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-170800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-822000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-105800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-363600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-189500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>357900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-102700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-200400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-169400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-217700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-412200</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>-104300</v>
       </c>
       <c r="R100" s="3">
         <v>-104300</v>
       </c>
       <c r="S100" s="3">
+        <v>-104300</v>
+      </c>
+      <c r="T100" s="3">
         <v>-367900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-18900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-69600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-124900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>510600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>53700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-41100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-131900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>586600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>20900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-411300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>250500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>520200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-7200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-60300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-36800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-74700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>555600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-100700</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-172100</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-26500</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-51000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-26900</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>47100</v>
+      </c>
+      <c r="E101" s="3">
         <v>19500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-50300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>35300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-3200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-19000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>26000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-13200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-5600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>19800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>87600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-90400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-81100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-19400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>87600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-90400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-81100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-19400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-2800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-34000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>8000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-13000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>53400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>25400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>12300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-35200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>27800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-19500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-9800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>7200</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-9000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-5200</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-33000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>26100</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-20000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>40400</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>18500</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>6500</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-31300</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-3400</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-113200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-422000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-13600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>321800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-379800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>482700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-434300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>410500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-60700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-55300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-712800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-196100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>236100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-216700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>425600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-115400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-296300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>326600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>373900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>155200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-146100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-718700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-45900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-364800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1169000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>958000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>300600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>558300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-122900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>368000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-230500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>382500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-197300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-59200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>145200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-230600</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>471600</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>29500</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-417700</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>148500</v>
       </c>
     </row>
